--- a/www/data-entry-template/GLATAR_data_entry_template_v21_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v21_long.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9498EE0-FB44-A645-B849-42D9E34BE179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3CB51A-EFC6-024E-9A6D-3D71C9C67F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -960,9 +960,6 @@
     <t>male, female, unknown, or both</t>
   </si>
   <si>
-    <t xml:space="preserve">fry, larva, nymph, pupa, juvenile, or adult </t>
-  </si>
-  <si>
     <t xml:space="preserve">wild or lab </t>
   </si>
   <si>
@@ -1198,6 +1195,9 @@
   </si>
   <si>
     <t>If there is no genus and species for the organism then use the next type of classifcation e.g., family ect. (Salvelinus); If validation does not return a valid scientific name and you have searched the taxonomic table but haven't found the species; please contact the database manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egg, fry, larva, nymph, pupa, juvenile, or adult </t>
   </si>
 </sst>
 </file>
@@ -1946,7 +1946,7 @@
         <v>178</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -1962,7 +1962,7 @@
         <v>157</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -1978,7 +1978,7 @@
         <v>144</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -1994,7 +1994,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -2044,7 +2044,7 @@
         <v>144</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -2333,14 +2333,14 @@
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="140" x14ac:dyDescent="0.2">
@@ -2354,11 +2354,11 @@
         <v>135</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2401,10 +2401,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="30" t="s">
         <v>263</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>264</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>244</v>
@@ -2419,13 +2419,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>179</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="F34" s="30"/>
     </row>
@@ -2443,7 +2443,7 @@
         <v>109</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F35" s="30"/>
     </row>
@@ -2455,10 +2455,10 @@
         <v>156</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
@@ -2471,7 +2471,7 @@
         <v>170</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>40</v>
@@ -2487,7 +2487,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>180</v>
@@ -2503,13 +2503,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="D39" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="D39" s="33" t="s">
-        <v>268</v>
-      </c>
       <c r="E39" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F39" s="30"/>
     </row>
@@ -2521,10 +2521,10 @@
         <v>171</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
@@ -2540,10 +2540,10 @@
         <v>233</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F41" s="30"/>
     </row>
@@ -2577,7 +2577,7 @@
         <v>12</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F43" s="30"/>
     </row>
@@ -2592,10 +2592,10 @@
         <v>63</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F44" s="30"/>
     </row>
@@ -2610,7 +2610,7 @@
         <v>141</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -2629,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F46" s="30"/>
     </row>
@@ -2676,7 +2676,7 @@
         <v>154</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -2692,7 +2692,7 @@
         <v>52</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -2708,7 +2708,7 @@
         <v>138</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -2724,11 +2724,11 @@
         <v>151</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
@@ -2742,11 +2742,11 @@
         <v>152</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="70" x14ac:dyDescent="0.2">
@@ -2757,13 +2757,13 @@
         <v>55</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F54" s="30"/>
     </row>
@@ -2775,10 +2775,10 @@
         <v>92</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -2791,14 +2791,14 @@
         <v>120</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
@@ -2815,10 +2815,10 @@
         <v>101</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2845,7 +2845,7 @@
         <v>118</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>220</v>
@@ -2861,7 +2861,7 @@
         <v>121</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>124</v>
@@ -2877,7 +2877,7 @@
         <v>122</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>125</v>
@@ -2893,7 +2893,7 @@
         <v>28</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D62" s="30" t="s">
         <v>41</v>
@@ -2909,7 +2909,7 @@
         <v>30</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>42</v>
@@ -2925,7 +2925,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D64" s="30" t="s">
         <v>43</v>
@@ -2941,7 +2941,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D65" s="30" t="s">
         <v>44</v>
@@ -2957,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D66" s="30" t="s">
         <v>45</v>
@@ -2973,7 +2973,7 @@
         <v>34</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D67" s="30" t="s">
         <v>46</v>
@@ -2995,7 +2995,7 @@
         <v>235</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F68" s="30"/>
     </row>
@@ -3007,7 +3007,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D69" s="30" t="s">
         <v>49</v>
@@ -3023,7 +3023,7 @@
         <v>36</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>50</v>
@@ -3039,7 +3039,7 @@
         <v>37</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D71" s="30" t="s">
         <v>51</v>
@@ -3055,7 +3055,7 @@
         <v>183</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>184</v>
@@ -3071,7 +3071,7 @@
         <v>186</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D73" s="30" t="s">
         <v>185</v>
@@ -3087,7 +3087,7 @@
         <v>126</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>127</v>
@@ -3103,7 +3103,7 @@
         <v>188</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D75" s="30" t="s">
         <v>189</v>
@@ -3125,7 +3125,7 @@
         <v>192</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F76" s="30"/>
     </row>
@@ -3143,7 +3143,7 @@
         <v>195</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F77" s="30"/>
     </row>
@@ -3155,7 +3155,7 @@
         <v>197</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D78" s="33" t="s">
         <v>198</v>
@@ -3171,13 +3171,13 @@
         <v>199</v>
       </c>
       <c r="C79" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="D79" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>304</v>
-      </c>
       <c r="E79" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F79" s="30"/>
     </row>
@@ -3195,7 +3195,7 @@
         <v>202</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F80" s="30"/>
     </row>
@@ -3223,13 +3223,13 @@
         <v>206</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F82" s="30"/>
     </row>
@@ -3247,7 +3247,7 @@
         <v>208</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F83" s="30"/>
     </row>
@@ -3281,7 +3281,7 @@
         <v>223</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F85" s="30"/>
     </row>
@@ -3296,7 +3296,7 @@
         <v>226</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="30"/>
@@ -3325,13 +3325,13 @@
         <v>213</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D88" s="30" t="s">
         <v>214</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F88" s="30"/>
     </row>
@@ -3343,10 +3343,10 @@
         <v>218</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E89" s="30"/>
       <c r="F89" s="30"/>
@@ -3362,7 +3362,7 @@
         <v>229</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3375,10 +3375,10 @@
         <v>216</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
@@ -44848,7 +44848,7 @@
       <formula1>"bulk, lipid free "</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
-      <formula1>"fry, larva, nymph, pupa, juvenile, adult "</formula1>
+      <formula1>"egg, fry, larva, nymph, pupa, juvenile, adult "</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
       <formula1>"male, female, unknown, both"</formula1>

--- a/www/data-entry-template/GLATAR_data_entry_template_v21_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v21_long.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3CB51A-EFC6-024E-9A6D-3D71C9C67F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134EB534-BD3C-7047-8EEA-35B49162D7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -966,9 +966,6 @@
     <t>fork, total, standard, or carapace</t>
   </si>
   <si>
-    <t>belly flap, blood, carcass, cleithra, eye lens, egg, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), or whole body (stomach removed)</t>
-  </si>
-  <si>
     <t>wet or dried</t>
   </si>
   <si>
@@ -1198,6 +1195,9 @@
   </si>
   <si>
     <t xml:space="preserve">egg, fry, larva, nymph, pupa, juvenile, or adult </t>
+  </si>
+  <si>
+    <t>belly flap, blood, carcass, cleithra, eye lens, egg, fin, gonad, heart, liver, muscle, otolith, scale, spines, stomach, viscera, whole body, whole body (gonads removed), or whole body (stomach removed)</t>
   </si>
 </sst>
 </file>
@@ -1946,7 +1946,7 @@
         <v>178</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -1962,7 +1962,7 @@
         <v>157</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -1978,7 +1978,7 @@
         <v>144</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -1994,7 +1994,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -2044,7 +2044,7 @@
         <v>144</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -2333,14 +2333,14 @@
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="140" x14ac:dyDescent="0.2">
@@ -2354,11 +2354,11 @@
         <v>135</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -2401,10 +2401,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" s="30" t="s">
         <v>262</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>263</v>
       </c>
       <c r="E33" s="30" t="s">
         <v>244</v>
@@ -2419,13 +2419,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>179</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F34" s="30"/>
     </row>
@@ -2455,10 +2455,10 @@
         <v>156</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
@@ -2471,7 +2471,7 @@
         <v>170</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>40</v>
@@ -2487,7 +2487,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>180</v>
@@ -2503,10 +2503,10 @@
         <v>97</v>
       </c>
       <c r="C39" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="D39" s="33" t="s">
         <v>266</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>267</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>246</v>
@@ -2521,10 +2521,10 @@
         <v>171</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
@@ -2540,10 +2540,10 @@
         <v>233</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F41" s="30"/>
     </row>
@@ -2577,7 +2577,7 @@
         <v>12</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="F43" s="30"/>
     </row>
@@ -2592,10 +2592,10 @@
         <v>63</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F44" s="30"/>
     </row>
@@ -2610,7 +2610,7 @@
         <v>141</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E45" s="30"/>
       <c r="F45" s="30"/>
@@ -2629,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F46" s="30"/>
     </row>
@@ -2676,7 +2676,7 @@
         <v>154</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -2692,7 +2692,7 @@
         <v>52</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -2708,7 +2708,7 @@
         <v>138</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -2724,11 +2724,11 @@
         <v>151</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
@@ -2742,11 +2742,11 @@
         <v>152</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="70" x14ac:dyDescent="0.2">
@@ -2757,13 +2757,13 @@
         <v>55</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F54" s="30"/>
     </row>
@@ -2775,10 +2775,10 @@
         <v>92</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -2791,14 +2791,14 @@
         <v>120</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="56" x14ac:dyDescent="0.2">
@@ -2815,10 +2815,10 @@
         <v>101</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -2845,7 +2845,7 @@
         <v>118</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>220</v>
@@ -2861,7 +2861,7 @@
         <v>121</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>124</v>
@@ -2877,7 +2877,7 @@
         <v>122</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>125</v>
@@ -2893,7 +2893,7 @@
         <v>28</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D62" s="30" t="s">
         <v>41</v>
@@ -2909,7 +2909,7 @@
         <v>30</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>42</v>
@@ -2925,7 +2925,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D64" s="30" t="s">
         <v>43</v>
@@ -2941,7 +2941,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D65" s="30" t="s">
         <v>44</v>
@@ -2957,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D66" s="30" t="s">
         <v>45</v>
@@ -2973,7 +2973,7 @@
         <v>34</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D67" s="30" t="s">
         <v>46</v>
@@ -2995,7 +2995,7 @@
         <v>235</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F68" s="30"/>
     </row>
@@ -3007,7 +3007,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D69" s="30" t="s">
         <v>49</v>
@@ -3023,7 +3023,7 @@
         <v>36</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>50</v>
@@ -3039,7 +3039,7 @@
         <v>37</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D71" s="30" t="s">
         <v>51</v>
@@ -3055,7 +3055,7 @@
         <v>183</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>184</v>
@@ -3071,7 +3071,7 @@
         <v>186</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D73" s="30" t="s">
         <v>185</v>
@@ -3087,7 +3087,7 @@
         <v>126</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>127</v>
@@ -3103,7 +3103,7 @@
         <v>188</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D75" s="30" t="s">
         <v>189</v>
@@ -3125,7 +3125,7 @@
         <v>192</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F76" s="30"/>
     </row>
@@ -3143,7 +3143,7 @@
         <v>195</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F77" s="30"/>
     </row>
@@ -3155,7 +3155,7 @@
         <v>197</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D78" s="33" t="s">
         <v>198</v>
@@ -3171,13 +3171,13 @@
         <v>199</v>
       </c>
       <c r="C79" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="D79" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>303</v>
-      </c>
       <c r="E79" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F79" s="30"/>
     </row>
@@ -3195,7 +3195,7 @@
         <v>202</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F80" s="30"/>
     </row>
@@ -3223,13 +3223,13 @@
         <v>206</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F82" s="30"/>
     </row>
@@ -3247,7 +3247,7 @@
         <v>208</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F83" s="30"/>
     </row>
@@ -3281,7 +3281,7 @@
         <v>223</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F85" s="30"/>
     </row>
@@ -3296,7 +3296,7 @@
         <v>226</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E86" s="30"/>
       <c r="F86" s="30"/>
@@ -3325,13 +3325,13 @@
         <v>213</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D88" s="30" t="s">
         <v>214</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F88" s="30"/>
     </row>
@@ -3343,10 +3343,10 @@
         <v>218</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E89" s="30"/>
       <c r="F89" s="30"/>
@@ -3362,7 +3362,7 @@
         <v>229</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
@@ -3375,10 +3375,10 @@
         <v>216</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
@@ -44800,13 +44800,10 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="21">
     <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="L5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI993:AI9991 AJ6:AJ992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
       <formula1>"Joules/g"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V993:V9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
-      <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F991" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
       <formula1>"spring, summer, fall, winter"</formula1>
@@ -44835,9 +44832,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL6:BL9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
       <formula1>"Th (free thiamine), TMP (thiamine monophosphate), TPP (thiamine pyrophosphate), TTh (total thiamine)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
-      <formula1>"belly flap, blood, carcass, cleithra, egg, eye lens, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:T10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
       <formula1>"Individual, Composite, Mean, SD, Equation"</formula1>
     </dataValidation>
@@ -44865,6 +44859,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI6:BI10000" xr:uid="{D97CB6FC-E274-3949-845D-05F3071BE316}">
       <formula1>"µg/mg sample weight, % total protein"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V100000" xr:uid="{EB48C38D-E958-9B47-91E0-AD83C95F9674}">
+      <formula1>"belly flap, blood, carcass, cleithra, eye lens, egg, fin, gonad, heart, liver, muscle, otolith, scales, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
